--- a/Profit Amount/purchase_data.xlsx
+++ b/Profit Amount/purchase_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alh\Profit Amount\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C0426B-4FAB-45E1-95C7-55CDC0D7B6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52B5D26D-D548-4FB1-94D4-1076D20BF2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,7 +424,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B353"/>
+  <dimension ref="A1:B352"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
@@ -438,7 +440,7 @@
         <v>2502184</v>
       </c>
       <c r="B2" s="1">
-        <v>4544.1295199849928</v>
+        <v>5038.8901591464391</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -446,7 +448,7 @@
         <v>2502174</v>
       </c>
       <c r="B3" s="1">
-        <v>4889.6901598484937</v>
+        <v>5829.4734668187148</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -462,7 +464,7 @@
         <v>2960184</v>
       </c>
       <c r="B5" s="1">
-        <v>13463.077008095332</v>
+        <v>14394.521339271621</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
@@ -470,7 +472,7 @@
         <v>2960222</v>
       </c>
       <c r="B6" s="1">
-        <v>10770.461606476261</v>
+        <v>11515.617071417299</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
@@ -478,7 +480,7 @@
         <v>7427213</v>
       </c>
       <c r="B7" s="1">
-        <v>4450.2716173271674</v>
+        <v>4725.819580703168</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
@@ -486,7 +488,7 @@
         <v>7428213</v>
       </c>
       <c r="B8" s="1">
-        <v>6080.636085275446</v>
+        <v>6113.0534927314457</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
@@ -494,7 +496,7 @@
         <v>7600184</v>
       </c>
       <c r="B9" s="1">
-        <v>4653.9712014858669</v>
+        <v>4677.1264925258674</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
@@ -502,7 +504,7 @@
         <v>7600203</v>
       </c>
       <c r="B10" s="1">
-        <v>2495.1562188663343</v>
+        <v>2620.1947904823342</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
@@ -510,7 +512,7 @@
         <v>7670213</v>
       </c>
       <c r="B11" s="1">
-        <v>3335.9118344795979</v>
+        <v>3368.329241935598</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -518,7 +520,7 @@
         <v>7688203</v>
       </c>
       <c r="B12" s="1">
-        <v>2854.4341593423005</v>
+        <v>3035.045429454301</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -526,7 +528,7 @@
         <v>7688213</v>
       </c>
       <c r="B13" s="1">
-        <v>3332.5564302579751</v>
+        <v>3543.269578721975</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
@@ -566,7 +568,7 @@
         <v>2968213</v>
       </c>
       <c r="B18" s="1">
-        <v>4040.7403894022186</v>
+        <v>4056.949093130218</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
@@ -590,7 +592,7 @@
         <v>7420213</v>
       </c>
       <c r="B21" s="1">
-        <v>4389.5137061179466</v>
+        <v>4713.6877806779457</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
@@ -598,7 +600,7 @@
         <v>7420222</v>
       </c>
       <c r="B22" s="1">
-        <v>5017.2476778379687</v>
+        <v>5387.7323344779679</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
@@ -606,7 +608,7 @@
         <v>7421234</v>
       </c>
       <c r="B23" s="1">
-        <v>6784.8342446600636</v>
+        <v>7247.940065460064</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
@@ -614,7 +616,7 @@
         <v>7477203</v>
       </c>
       <c r="B24" s="1">
-        <v>3583.8025595669692</v>
+        <v>3806.0933535509694</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
@@ -638,7 +640,7 @@
         <v>7638234</v>
       </c>
       <c r="B27" s="1">
-        <v>6091.0927691060424</v>
+        <v>6345.8009705460427</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
@@ -654,7 +656,7 @@
         <v>2586184</v>
       </c>
       <c r="B29" s="1">
-        <v>13294.676323572347</v>
+        <v>12405.349902834514</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
@@ -662,7 +664,7 @@
         <v>7267234</v>
       </c>
       <c r="B30" s="1">
-        <v>13833.135289485521</v>
+        <v>13339.916591570276</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
@@ -670,7 +672,7 @@
         <v>7264222</v>
       </c>
       <c r="B31" s="1">
-        <v>4868.9932503597101</v>
+        <v>4799.6274080970024</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
@@ -678,7 +680,7 @@
         <v>7265234</v>
       </c>
       <c r="B32" s="1">
-        <v>8801.8664981536185</v>
+        <v>8697.9261015216252</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
@@ -686,7 +688,7 @@
         <v>7677282</v>
       </c>
       <c r="B33" s="1">
-        <v>2459.5603419480526</v>
+        <v>2663.3269031000527</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
@@ -694,7 +696,7 @@
         <v>7677283</v>
       </c>
       <c r="B34" s="1">
-        <v>3541.0516596092125</v>
+        <v>3837.4393849212129</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
@@ -702,7 +704,7 @@
         <v>7677184</v>
       </c>
       <c r="B35" s="1">
-        <v>4670.8913682107295</v>
+        <v>4925.5995696507307</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
@@ -710,7 +712,7 @@
         <v>2896150</v>
       </c>
       <c r="B36" s="1">
-        <v>2264.8992045726586</v>
+        <v>2293.8451707959421</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -718,7 +720,7 @@
         <v>2896185</v>
       </c>
       <c r="B37" s="1">
-        <v>2491.1843912447939</v>
+        <v>2523.0223375425185</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
@@ -726,7 +728,7 @@
         <v>2927152</v>
       </c>
       <c r="B38" s="1">
-        <v>4430.2913885072394</v>
+        <v>4555.3299601232393</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
@@ -734,7 +736,7 @@
         <v>2927184</v>
       </c>
       <c r="B39" s="1">
-        <v>4922.5459872302708</v>
+        <v>5061.4777334702703</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
@@ -742,7 +744,7 @@
         <v>2933156</v>
       </c>
       <c r="B40" s="1">
-        <v>3771.8633522671312</v>
+        <v>4160.8722417391309</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
@@ -750,7 +752,7 @@
         <v>1404184</v>
       </c>
       <c r="B41" s="1">
-        <v>4957.7074772072883</v>
+        <v>6301.0543753153961</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
@@ -758,7 +760,7 @@
         <v>1404234</v>
       </c>
       <c r="B42" s="1">
-        <v>4888.2429345353667</v>
+        <v>6226.5907269713334</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
@@ -766,7 +768,7 @@
         <v>1404242</v>
       </c>
       <c r="B43" s="1">
-        <v>2433.8304239088802</v>
+        <v>3102.0482499336972</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
@@ -774,7 +776,7 @@
         <v>1404265</v>
       </c>
       <c r="B44" s="1">
-        <v>4818.5156803692507</v>
+        <v>6151.6228976749371</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
@@ -782,7 +784,7 @@
         <v>5034184</v>
       </c>
       <c r="B45" s="1">
-        <v>3549.2054323210828</v>
+        <v>4031.4713537927946</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
@@ -790,7 +792,7 @@
         <v>5034203</v>
       </c>
       <c r="B46" s="1">
-        <v>2101.5493140221251</v>
+        <v>2631.2465334639423</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
@@ -798,7 +800,7 @@
         <v>5034229</v>
       </c>
       <c r="B47" s="1">
-        <v>3549.2054323210805</v>
+        <v>4431.3935203139727</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
@@ -806,7 +808,7 @@
         <v>7231256</v>
       </c>
       <c r="B48" s="1">
-        <v>3255.1946197103562</v>
+        <v>3970.230836593294</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
@@ -814,7 +816,7 @@
         <v>7429184</v>
       </c>
       <c r="B49" s="1">
-        <v>4734.1377782340487</v>
+        <v>5672.9544371639595</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
@@ -822,7 +824,7 @@
         <v>7429240</v>
       </c>
       <c r="B50" s="1">
-        <v>4726.6187940898499</v>
+        <v>5665.4056396013902</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
@@ -830,7 +832,7 @@
         <v>7429244</v>
       </c>
       <c r="B51" s="1">
-        <v>5689.149668437195</v>
+        <v>6508.0440462303441</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -838,7 +840,7 @@
         <v>7429297</v>
       </c>
       <c r="B52" s="1">
-        <v>1632.4164042343466</v>
+        <v>1944.6513568599044</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
@@ -846,7 +848,7 @@
         <v>7430184</v>
       </c>
       <c r="B53" s="1">
-        <v>4854.97298066028</v>
+        <v>5900.7659156377167</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
@@ -854,7 +856,7 @@
         <v>7430234</v>
       </c>
       <c r="B54" s="1">
-        <v>4425.374011985833</v>
+        <v>5748.5036055519786</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
@@ -862,7 +864,7 @@
         <v>7430240</v>
       </c>
       <c r="B55" s="1">
-        <v>4541.1504671858302</v>
+        <v>5748.5036055519749</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
@@ -870,7 +872,7 @@
         <v>7430296</v>
       </c>
       <c r="B56" s="1">
-        <v>1482.726258101814</v>
+        <v>1936.7118000248479</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
@@ -878,7 +880,7 @@
         <v>7430297</v>
       </c>
       <c r="B57" s="1">
-        <v>1523.2480174218138</v>
+        <v>1936.7118000248479</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
@@ -886,7 +888,7 @@
         <v>7434256</v>
       </c>
       <c r="B58" s="1">
-        <v>3219.0565901647801</v>
+        <v>4000.000205456538</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
@@ -894,7 +896,7 @@
         <v>7436184</v>
       </c>
       <c r="B59" s="1">
-        <v>4712.2466238171573</v>
+        <v>5592.4498402620993</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
@@ -902,7 +904,7 @@
         <v>7436229</v>
       </c>
       <c r="B60" s="1">
-        <v>4897.4889521371533</v>
+        <v>5777.6921685820953</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -910,7 +912,7 @@
         <v>7436250</v>
       </c>
       <c r="B61" s="1">
-        <v>1680.8773035647291</v>
+        <v>2027.9381602920907</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -918,7 +920,7 @@
         <v>7436253</v>
       </c>
       <c r="B62" s="1">
-        <v>3305.888931564778</v>
+        <v>4000.0002054565352</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
@@ -926,7 +928,7 @@
         <v>7470184</v>
       </c>
       <c r="B63" s="1">
-        <v>4267.5181008101599</v>
+        <v>5239.1273751396211</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
@@ -934,7 +936,7 @@
         <v>7470251</v>
       </c>
       <c r="B64" s="1">
-        <v>1515.4830989986046</v>
+        <v>1716.8922288100418</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -942,7 +944,7 @@
         <v>7470256</v>
       </c>
       <c r="B65" s="1">
-        <v>3019.8655235979804</v>
+        <v>3423.7600556008269</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -950,7 +952,7 @@
         <v>7472184</v>
       </c>
       <c r="B66" s="1">
-        <v>4020.4427469108073</v>
+        <v>4993.393957286492</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
@@ -958,7 +960,7 @@
         <v>7472203</v>
       </c>
       <c r="B67" s="1">
-        <v>2369.6402915456893</v>
+        <v>2953.2084355049692</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
@@ -966,7 +968,7 @@
         <v>7472234</v>
       </c>
       <c r="B68" s="1">
-        <v>3920.6044790416822</v>
+        <v>4894.3333113978188</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
@@ -974,7 +976,7 @@
         <v>7472251</v>
       </c>
       <c r="B69" s="1">
-        <v>1400.0115334992238</v>
+        <v>1765.0678708004878</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
@@ -982,7 +984,7 @@
         <v>7472256</v>
       </c>
       <c r="B70" s="1">
-        <v>2760.0812457474144</v>
+        <v>3490.4684514526375</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -990,7 +992,7 @@
         <v>7485174</v>
       </c>
       <c r="B71" s="1">
-        <v>4304.0621989058836</v>
+        <v>5192.1358987753247</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
@@ -998,7 +1000,7 @@
         <v>7485184</v>
       </c>
       <c r="B72" s="1">
-        <v>3895.1867584933566</v>
+        <v>4990.5968907500237</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
@@ -1006,7 +1008,7 @@
         <v>7485234</v>
       </c>
       <c r="B73" s="1">
-        <v>3594.9533728145088</v>
+        <v>4597.7048793786689</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
@@ -1014,7 +1016,7 @@
         <v>7485242</v>
       </c>
       <c r="B74" s="1">
-        <v>1756.3659611725848</v>
+        <v>2257.474453436359</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
@@ -1022,7 +1024,7 @@
         <v>7485251</v>
       </c>
       <c r="B75" s="1">
-        <v>1327.9884797438958</v>
+        <v>1703.9071847635328</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
@@ -1030,7 +1032,7 @@
         <v>7485265</v>
       </c>
       <c r="B76" s="1">
-        <v>3424.7779258921587</v>
+        <v>4426.5586869106482</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
@@ -1038,7 +1040,7 @@
         <v>7489184</v>
       </c>
       <c r="B77" s="1">
-        <v>4639.2403292637373</v>
+        <v>5574.082906424148</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1046,7 +1048,7 @@
         <v>7489203</v>
       </c>
       <c r="B78" s="1">
-        <v>2759.5051899377131</v>
+        <v>3320.6893422656026</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
@@ -1054,7 +1056,7 @@
         <v>7489234</v>
       </c>
       <c r="B79" s="1">
-        <v>4575.8815640775829</v>
+        <v>5280.2492685832431</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
@@ -1062,7 +1064,7 @@
         <v>7489241</v>
       </c>
       <c r="B80" s="1">
-        <v>2151.0885236924387</v>
+        <v>2619.0856608130548</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
@@ -1070,7 +1072,7 @@
         <v>7489250</v>
       </c>
       <c r="B81" s="1">
-        <v>1620.6204970293077</v>
+        <v>1971.3891090887669</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
@@ -1078,7 +1080,7 @@
         <v>7489253</v>
       </c>
       <c r="B82" s="1">
-        <v>3194.2015045311623</v>
+        <v>3896.5960392506768</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
@@ -1086,7 +1088,7 @@
         <v>7489265</v>
       </c>
       <c r="B83" s="1">
-        <v>4360.0754427086522</v>
+        <v>5181.0866169656756</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
@@ -1094,7 +1096,7 @@
         <v>7494174</v>
       </c>
       <c r="B84" s="1">
-        <v>5166.4516323735916</v>
+        <v>6059.6422559606099</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
@@ -1102,7 +1104,7 @@
         <v>7494184</v>
       </c>
       <c r="B85" s="1">
-        <v>4788.5420538760764</v>
+        <v>5680.0599050941237</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
@@ -1110,7 +1112,7 @@
         <v>7494234</v>
       </c>
       <c r="B86" s="1">
-        <v>4779.6823352097817</v>
+        <v>5671.0159350674749</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
@@ -1118,7 +1120,7 @@
         <v>7494242</v>
       </c>
       <c r="B87" s="1">
-        <v>2370.0209442204491</v>
+        <v>2582.1737857580106</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
@@ -1126,7 +1128,7 @@
         <v>7494251</v>
       </c>
       <c r="B88" s="1">
-        <v>1787.8151311149036</v>
+        <v>2122.0269840740852</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
@@ -1134,7 +1136,7 @@
         <v>7494265</v>
       </c>
       <c r="B89" s="1">
-        <v>4728.9699578131449</v>
+        <v>5619.5874724461737</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
@@ -1142,7 +1144,7 @@
         <v>7505195</v>
       </c>
       <c r="B90" s="1">
-        <v>2171.4493594063674</v>
+        <v>2875.5606488516682</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
@@ -1150,7 +1152,7 @@
         <v>7530228</v>
       </c>
       <c r="B91" s="1">
-        <v>5571.3498344402469</v>
+        <v>5962.9675147772668</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
@@ -1158,7 +1160,7 @@
         <v>7556184</v>
       </c>
       <c r="B92" s="1">
-        <v>4745.4524905185071</v>
+        <v>5684.0405939708207</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
@@ -1166,7 +1168,7 @@
         <v>7556203</v>
       </c>
       <c r="B93" s="1">
-        <v>2296.9535407935473</v>
+        <v>3012.6539663169256</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
@@ -1174,7 +1176,7 @@
         <v>7556204</v>
       </c>
       <c r="B94" s="1">
-        <v>2296.9535407935459</v>
+        <v>3012.6539663169242</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
@@ -1182,7 +1184,7 @@
         <v>7556234</v>
       </c>
       <c r="B95" s="1">
-        <v>4414.304746767556</v>
+        <v>5328.9552655213329</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
         <v>7556241</v>
       </c>
       <c r="B96" s="1">
-        <v>1888.9760333290897</v>
+        <v>2519.9966013218473</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
@@ -1198,7 +1200,7 @@
         <v>7556242</v>
       </c>
       <c r="B97" s="1">
-        <v>1888.9760333290908</v>
+        <v>2404.2201461218488</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
@@ -1206,7 +1208,7 @@
         <v>7556250</v>
       </c>
       <c r="B98" s="1">
-        <v>1410.9462417416055</v>
+        <v>1858.2224287064848</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
@@ -1214,7 +1216,7 @@
         <v>7556251</v>
       </c>
       <c r="B99" s="1">
-        <v>1410.9462417416064</v>
+        <v>1771.3900873064854</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
@@ -1222,7 +1224,7 @@
         <v>7556253</v>
       </c>
       <c r="B100" s="1">
-        <v>2698.9964670127047</v>
+        <v>3680.437640053844</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
@@ -1230,7 +1232,7 @@
         <v>7556265</v>
       </c>
       <c r="B101" s="1">
-        <v>3819.8966460070164</v>
+        <v>4781.0804595320296</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
@@ -1238,7 +1240,7 @@
         <v>7577174</v>
       </c>
       <c r="B102" s="1">
-        <v>4906.0855744997116</v>
+        <v>5821.9691305546494</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
@@ -1246,7 +1248,7 @@
         <v>7577184</v>
       </c>
       <c r="B103" s="1">
-        <v>4755.3833906091277</v>
+        <v>5670.595682233602</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
@@ -1254,7 +1256,7 @@
         <v>7577203</v>
       </c>
       <c r="B104" s="1">
-        <v>2605.6884023704497</v>
+        <v>3224.0223985284065</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
@@ -1262,7 +1264,7 @@
         <v>7577234</v>
       </c>
       <c r="B105" s="1">
-        <v>4063.4980490718117</v>
+        <v>5140.1742796908902</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
@@ -1270,7 +1272,7 @@
         <v>7577242</v>
       </c>
       <c r="B106" s="1">
-        <v>2042.2035736841437</v>
+        <v>2557.2760645617259</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
@@ -1278,7 +1280,7 @@
         <v>7577251</v>
       </c>
       <c r="B107" s="1">
-        <v>1531.5557487807669</v>
+        <v>1917.9264156195916</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
@@ -1286,7 +1288,7 @@
         <v>7577256</v>
       </c>
       <c r="B108" s="1">
-        <v>3142.3990366187704</v>
+        <v>3914.9514842377662</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
@@ -1294,7 +1296,7 @@
         <v>7577265</v>
       </c>
       <c r="B109" s="1">
-        <v>3970.2816506832505</v>
+        <v>4999.9799806104429</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
@@ -1302,7 +1304,7 @@
         <v>2502234</v>
       </c>
       <c r="B110" s="1">
-        <v>4447.0947648498823</v>
+        <v>4942.079565478105</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
@@ -1310,7 +1312,7 @@
         <v>2502265</v>
       </c>
       <c r="B111" s="1">
-        <v>4375.1072859319875</v>
+        <v>5312.8157831622775</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
@@ -1318,7 +1320,7 @@
         <v>2503184</v>
       </c>
       <c r="B112" s="1">
-        <v>4873.1642953518822</v>
+        <v>5814.1306634408738</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
@@ -1326,7 +1328,7 @@
         <v>2503234</v>
       </c>
       <c r="B113" s="1">
-        <v>4768.6214268930262</v>
+        <v>5708.2195749332222</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
@@ -1334,7 +1336,7 @@
         <v>2503265</v>
       </c>
       <c r="B114" s="1">
-        <v>4703.7697356984827</v>
+        <v>5197.8479244615837</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
@@ -1342,7 +1344,7 @@
         <v>4906175</v>
       </c>
       <c r="B115" s="1">
-        <v>2506.0032070660641</v>
+        <v>3034.5128114497988</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
@@ -1350,7 +1352,7 @@
         <v>4906184</v>
       </c>
       <c r="B116" s="1">
-        <v>4800.6287459029954</v>
+        <v>5856.1312978246879</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
@@ -1358,7 +1360,7 @@
         <v>4906234</v>
       </c>
       <c r="B117" s="1">
-        <v>4673.4129695934216</v>
+        <v>5728.5310916825647</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
@@ -1366,7 +1368,7 @@
         <v>7511184</v>
       </c>
       <c r="B118" s="1">
-        <v>4838.1014645755104</v>
+        <v>5780.1210330241765</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
@@ -1374,7 +1376,7 @@
         <v>7511234</v>
       </c>
       <c r="B119" s="1">
-        <v>4562.6870110754826</v>
+        <v>5503.3035631560942</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
@@ -1382,7 +1384,7 @@
         <v>7511240</v>
       </c>
       <c r="B120" s="1">
-        <v>4562.6870110754789</v>
+        <v>5503.3035631560888</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
@@ -1390,7 +1392,7 @@
         <v>7511251</v>
       </c>
       <c r="B121" s="1">
-        <v>1687.1695505307509</v>
+        <v>2039.875883656767</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
@@ -1398,7 +1400,7 @@
         <v>7511269</v>
       </c>
       <c r="B122" s="1">
-        <v>4126.1082095855772</v>
+        <v>5066.1544468478724</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
@@ -1406,7 +1408,7 @@
         <v>7515184</v>
       </c>
       <c r="B123" s="1">
-        <v>5411.7999547776653</v>
+        <v>6356.9476293811549</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
@@ -1414,7 +1416,7 @@
         <v>7515240</v>
       </c>
       <c r="B124" s="1">
-        <v>5093.7265900306247</v>
+        <v>5590.6070480101189</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
@@ -1422,7 +1424,7 @@
         <v>7515265</v>
       </c>
       <c r="B125" s="1">
-        <v>4666.8635843174116</v>
+        <v>5610.2148856687827</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
@@ -1430,7 +1432,7 @@
         <v>7515269</v>
       </c>
       <c r="B126" s="1">
-        <v>4666.8635843174088</v>
+        <v>5610.2148856687809</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
@@ -1438,7 +1440,7 @@
         <v>3723213</v>
       </c>
       <c r="B127" s="1">
-        <v>2881.3545494492546</v>
+        <v>3233.6963406652053</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
@@ -1446,7 +1448,7 @@
         <v>3725213</v>
       </c>
       <c r="B128" s="1">
-        <v>2289.1375498143502</v>
+        <v>3041.4634946188135</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
@@ -1454,7 +1456,7 @@
         <v>4950184</v>
       </c>
       <c r="B129" s="1">
-        <v>4188.0807558012448</v>
+        <v>5102.4175282106826</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
@@ -1462,7 +1464,7 @@
         <v>4950234</v>
       </c>
       <c r="B130" s="1">
-        <v>3639.9651190866239</v>
+        <v>4692.6812977029913</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
@@ -1470,7 +1472,7 @@
         <v>4950269</v>
       </c>
       <c r="B131" s="1">
-        <v>3579.9169243373794</v>
+        <v>4181.0542128768166</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
@@ -1478,7 +1480,7 @@
         <v>7553213</v>
       </c>
       <c r="B132" s="1">
-        <v>2702.3115687929003</v>
+        <v>3595.3396488694348</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
@@ -1486,7 +1488,7 @@
         <v>7554251</v>
       </c>
       <c r="B133" s="1">
-        <v>1839.0438724828896</v>
+        <v>2173.7415351827208</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
@@ -1494,7 +1496,7 @@
         <v>7554252</v>
       </c>
       <c r="B134" s="1">
-        <v>2086.7989295426669</v>
+        <v>2466.0439228107716</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
@@ -1502,7 +1504,7 @@
         <v>7563250</v>
       </c>
       <c r="B135" s="1">
-        <v>1371.7920248543546</v>
+        <v>1783.4774188511433</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
@@ -1510,7 +1512,7 @@
         <v>7227251</v>
       </c>
       <c r="B136" s="1">
-        <v>1609.5618470991069</v>
+        <v>2062.7231947263276</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
@@ -1518,7 +1520,7 @@
         <v>7227252</v>
       </c>
       <c r="B137" s="1">
-        <v>1766.6857416211858</v>
+        <v>2171.9842171946993</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
@@ -1526,7 +1528,7 @@
         <v>7651265</v>
       </c>
       <c r="B138" s="1">
-        <v>4005.3190079707329</v>
+        <v>4478.5293825552008</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
@@ -1534,7 +1536,7 @@
         <v>7586234</v>
       </c>
       <c r="B139" s="1">
-        <v>4055.1471599198858</v>
+        <v>4921.2788602779356</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
@@ -1542,7 +1544,7 @@
         <v>7586242</v>
       </c>
       <c r="B140" s="1">
-        <v>1997.7134805424294</v>
+        <v>2430.6157441534124</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
@@ -1550,7 +1552,7 @@
         <v>7586265</v>
       </c>
       <c r="B141" s="1">
-        <v>3915.0561370481346</v>
+        <v>4781.1366420584736</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
@@ -1558,7 +1560,7 @@
         <v>7226184</v>
       </c>
       <c r="B142" s="1">
-        <v>4516.0739335715816</v>
+        <v>4585.9236056405698</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
@@ -1566,7 +1568,7 @@
         <v>7226251</v>
       </c>
       <c r="B143" s="1">
-        <v>1722.4167823625112</v>
+        <v>1747.5369584609987</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
@@ -1574,7 +1576,7 @@
         <v>2824152</v>
       </c>
       <c r="B144" s="1">
-        <v>3840.030968265291</v>
+        <v>4818.1595812315127</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
@@ -1582,7 +1584,7 @@
         <v>2824184</v>
       </c>
       <c r="B145" s="1">
-        <v>4262.0892974964063</v>
+        <v>5209.640575885529</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
@@ -1590,7 +1592,7 @@
         <v>2825185</v>
       </c>
       <c r="B146" s="1">
-        <v>4056.7096594931218</v>
+        <v>4528.0963054001177</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
@@ -1598,7 +1600,7 @@
         <v>2825258</v>
       </c>
       <c r="B147" s="1">
-        <v>5214.4742114931205</v>
+        <v>5685.8608574001155</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
@@ -1606,7 +1608,7 @@
         <v>2825022</v>
       </c>
       <c r="B148" s="1">
-        <v>6244.3075858248976</v>
+        <v>6809.6128020567867</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
@@ -1614,7 +1616,7 @@
         <v>2825195</v>
       </c>
       <c r="B149" s="1">
-        <v>5720.922969479424</v>
+        <v>6180.5326235129642</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
@@ -1622,7 +1624,7 @@
         <v>2825030</v>
       </c>
       <c r="B150" s="1">
-        <v>6400.1193037555204</v>
+        <v>6915.0223709007259</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
@@ -1630,7 +1632,7 @@
         <v>2828152</v>
       </c>
       <c r="B151" s="1">
-        <v>4622.3034169463608</v>
+        <v>5460.5880215239831</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
@@ -1638,7 +1640,7 @@
         <v>2828184</v>
       </c>
       <c r="B152" s="1">
-        <v>5075.3601365668492</v>
+        <v>6005.9825102484401</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
@@ -1646,7 +1648,7 @@
         <v>2828229</v>
       </c>
       <c r="B153" s="1">
-        <v>5191.1365917668463</v>
+        <v>6121.7589654484373</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
@@ -1654,7 +1656,7 @@
         <v>2828230</v>
       </c>
       <c r="B154" s="1">
-        <v>4726.5022266263613</v>
+        <v>5192.8785941389378</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
@@ -1662,7 +1664,7 @@
         <v>2829152</v>
       </c>
       <c r="B155" s="1">
-        <v>4622.3034169463608</v>
+        <v>5088.6797844589391</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
@@ -1670,7 +1672,7 @@
         <v>2829184</v>
       </c>
       <c r="B156" s="1">
-        <v>5075.3601365668492</v>
+        <v>6005.9825102484401</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
@@ -1678,7 +1680,7 @@
         <v>2829229</v>
       </c>
       <c r="B157" s="1">
-        <v>5191.1365917668463</v>
+        <v>6121.7589654484373</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
@@ -1686,7 +1688,7 @@
         <v>2829230</v>
       </c>
       <c r="B158" s="1">
-        <v>4726.5022266263613</v>
+        <v>5564.7868312039836</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
@@ -1694,7 +1696,7 @@
         <v>2830230</v>
       </c>
       <c r="B159" s="1">
-        <v>4726.5022266263613</v>
+        <v>5564.7868312039836</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
@@ -1702,7 +1704,7 @@
         <v>2830229</v>
       </c>
       <c r="B160" s="1">
-        <v>5191.1365917668463</v>
+        <v>6121.7589654484373</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
@@ -1710,7 +1712,7 @@
         <v>2885036</v>
       </c>
       <c r="B161" s="1">
-        <v>3822.1591200598405</v>
+        <v>4311.9623114875749</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
@@ -1718,7 +1720,7 @@
         <v>2889156</v>
       </c>
       <c r="B162" s="1">
-        <v>3491.0200556184018</v>
+        <v>4168.2522835405971</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
@@ -1726,7 +1728,7 @@
         <v>2924152</v>
       </c>
       <c r="B163" s="1">
-        <v>3969.0090810208831</v>
+        <v>4493.7032617270115</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
@@ -1734,7 +1736,7 @@
         <v>2924184</v>
       </c>
       <c r="B164" s="1">
-        <v>4409.4866801497137</v>
+        <v>5393.3107266625475</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
@@ -1742,7 +1744,7 @@
         <v>2924229</v>
       </c>
       <c r="B165" s="1">
-        <v>4687.35017262971</v>
+        <v>5648.018928102545</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
@@ -1750,7 +1752,7 @@
         <v>2924230</v>
       </c>
       <c r="B166" s="1">
-        <v>4219.0862242528829</v>
+        <v>5083.8552186611059</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
@@ -1758,7 +1760,7 @@
         <v>2931184</v>
       </c>
       <c r="B167" s="1">
-        <v>4612.8896767411643</v>
+        <v>5666.9737473076257</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
@@ -1766,7 +1768,7 @@
         <v>2931225</v>
       </c>
       <c r="B168" s="1">
-        <v>5659.5461939886427</v>
+        <v>6785.8252094843565</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
@@ -1774,7 +1776,7 @@
         <v>2931229</v>
       </c>
       <c r="B169" s="1">
-        <v>4728.6661319411614</v>
+        <v>5666.9737473076211</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
@@ -1782,7 +1784,7 @@
         <v>2936152</v>
       </c>
       <c r="B170" s="1">
-        <v>3962.862246456863</v>
+        <v>4911.2247021790854</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
@@ -1790,7 +1792,7 @@
         <v>2936229</v>
       </c>
       <c r="B171" s="1">
-        <v>4392.9979386866498</v>
+        <v>5446.3784088511748</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
@@ -1798,7 +1800,7 @@
         <v>2936230</v>
       </c>
       <c r="B172" s="1">
-        <v>3962.862246456863</v>
+        <v>4911.2247021790854</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
@@ -1806,7 +1808,7 @@
         <v>2944229</v>
       </c>
       <c r="B173" s="1">
-        <v>5077.8368847771726</v>
+        <v>5995.7346464054117</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
@@ -1814,7 +1816,7 @@
         <v>2944230</v>
       </c>
       <c r="B174" s="1">
-        <v>4574.4930205513483</v>
+        <v>5400.1948653319969</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
@@ -1822,7 +1824,7 @@
         <v>2949184</v>
       </c>
       <c r="B175" s="1">
-        <v>6817.9424804126784</v>
+        <v>7733.3679704547776</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
@@ -1830,7 +1832,7 @@
         <v>2971195</v>
       </c>
       <c r="B176" s="1">
-        <v>2298.5444722776951</v>
+        <v>2750.2670594597594</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
@@ -1838,7 +1840,7 @@
         <v>2971225</v>
       </c>
       <c r="B177" s="1">
-        <v>5701.3969838122757</v>
+        <v>6786.7296033473222</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
@@ -1846,7 +1848,7 @@
         <v>2967204</v>
       </c>
       <c r="B178" s="1">
-        <v>3401.9379331111991</v>
+        <v>3962.3770822778779</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
@@ -1854,7 +1856,7 @@
         <v>2967213</v>
       </c>
       <c r="B179" s="1">
-        <v>3798.1642417144849</v>
+        <v>4451.9285272228826</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
@@ -1862,7 +1864,7 @@
         <v>2967111</v>
       </c>
       <c r="B180" s="1">
-        <v>3879.207760354484</v>
+        <v>4614.0155645028808</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
@@ -1870,7 +1872,7 @@
         <v>2967184</v>
       </c>
       <c r="B181" s="1">
-        <v>5947.8650476219191</v>
+        <v>6882.6578689676671</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
@@ -1878,7 +1880,7 @@
         <v>7211213</v>
       </c>
       <c r="B182" s="1">
-        <v>3702.9960878472775</v>
+        <v>4380.8896068628692</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
@@ -1886,7 +1888,7 @@
         <v>7271213</v>
       </c>
       <c r="B183" s="1">
-        <v>5357.0393949518057</v>
+        <v>5845.8888476102129</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
@@ -1894,7 +1896,7 @@
         <v>7271111</v>
       </c>
       <c r="B184" s="1">
-        <v>5357.0393949518029</v>
+        <v>6007.9758848902111</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
@@ -1902,7 +1904,7 @@
         <v>7275185</v>
       </c>
       <c r="B185" s="1">
-        <v>6331.9834077588512</v>
+        <v>6802.2005152370475</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
@@ -1910,7 +1912,7 @@
         <v>7275111</v>
       </c>
       <c r="B186" s="1">
-        <v>8862.4864824384858</v>
+        <v>9520.2201363980239</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
@@ -1918,7 +1920,7 @@
         <v>7275220</v>
       </c>
       <c r="B187" s="1">
-        <v>10128.883163990255</v>
+        <v>10881.167321186656</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
@@ -1926,7 +1928,7 @@
         <v>2900103</v>
       </c>
       <c r="B188" s="1">
-        <v>3755.9771734860146</v>
+        <v>4296.0206928565385</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
@@ -1934,7 +1936,7 @@
         <v>2900125</v>
       </c>
       <c r="B189" s="1">
-        <v>3448.7677875848408</v>
+        <v>3987.280342690734</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
@@ -1942,7 +1944,7 @@
         <v>2900145</v>
       </c>
       <c r="B190" s="1">
-        <v>3259.5430396282545</v>
+        <v>3796.8591891034157</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
@@ -1950,7 +1952,7 @@
         <v>2900165</v>
       </c>
       <c r="B191" s="1">
-        <v>1345.5104358817207</v>
+        <v>1569.1470334342432</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
@@ -1958,7 +1960,7 @@
         <v>2900175</v>
       </c>
       <c r="B192" s="1">
-        <v>2655.4660416801403</v>
+        <v>2882.2913669205836</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
@@ -1966,7 +1968,7 @@
         <v>2900184</v>
       </c>
       <c r="B193" s="1">
-        <v>5201.6767142365943</v>
+        <v>5640.0458078693619</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
@@ -1974,7 +1976,7 @@
         <v>7701341</v>
       </c>
       <c r="B194" s="1">
-        <v>4668.1256783887466</v>
+        <v>5090.2729971709668</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
@@ -1982,7 +1984,7 @@
         <v>7705303</v>
       </c>
       <c r="B195" s="1">
-        <v>2660.6233266398513</v>
+        <v>3111.4034631784775</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
@@ -1990,7 +1992,7 @@
         <v>7705313</v>
       </c>
       <c r="B196" s="1">
-        <v>2648.1218831229958</v>
+        <v>3098.777461071717</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
@@ -1998,7 +2000,7 @@
         <v>7705327</v>
       </c>
       <c r="B197" s="1">
-        <v>3113.695385659496</v>
+        <v>3653.6789359659269</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
@@ -2006,7 +2008,7 @@
         <v>7705337</v>
       </c>
       <c r="B198" s="1">
-        <v>3069.0471142702363</v>
+        <v>3608.9714559087838</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
@@ -2014,7 +2016,7 @@
         <v>7705339</v>
       </c>
       <c r="B199" s="1">
-        <v>1243.6050935134888</v>
+        <v>1468.2774477403989</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
@@ -2022,7 +2024,7 @@
         <v>7705340</v>
       </c>
       <c r="B200" s="1">
-        <v>2487.2101870269776</v>
+        <v>2936.5548954807978</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
@@ -2030,7 +2032,7 @@
         <v>7705341</v>
       </c>
       <c r="B201" s="1">
-        <v>4539.6280107245775</v>
+        <v>5437.8405805198063</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
@@ -2038,7 +2040,7 @@
         <v>7727303</v>
       </c>
       <c r="B202" s="1">
-        <v>2891.4285572054896</v>
+        <v>3209.8872324710637</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
@@ -2046,7 +2048,7 @@
         <v>7727313</v>
       </c>
       <c r="B203" s="1">
-        <v>2732.3413471415688</v>
+        <v>3324.3270522241755</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
@@ -2054,7 +2056,7 @@
         <v>7727327</v>
       </c>
       <c r="B204" s="1">
-        <v>3190.8320666725658</v>
+        <v>3900.0299845122972</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
@@ -2062,7 +2064,7 @@
         <v>7727337</v>
       </c>
       <c r="B205" s="1">
-        <v>3090.4672168731086</v>
+        <v>3867.4409596544388</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
@@ -2070,7 +2072,7 @@
         <v>7727341</v>
       </c>
       <c r="B206" s="1">
-        <v>4924.3735234813839</v>
+        <v>6217.9525985533519</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
@@ -2078,7 +2080,7 @@
         <v>7849303</v>
       </c>
       <c r="B207" s="1">
-        <v>2914.9269443136859</v>
+        <v>3287.9245088982116</v>
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
@@ -2086,7 +2088,7 @@
         <v>7849313</v>
       </c>
       <c r="B208" s="1">
-        <v>3437.8607310672355</v>
+        <v>3890.0740753337336</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
@@ -2094,7 +2096,7 @@
         <v>7849327</v>
       </c>
       <c r="B209" s="1">
-        <v>3349.9387252186471</v>
+        <v>4031.4256672261831</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
@@ -2102,7 +2104,7 @@
         <v>7849337</v>
       </c>
       <c r="B210" s="1">
-        <v>3316.4004323287154</v>
+        <v>3997.8025205948479</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
@@ -2110,7 +2112,7 @@
         <v>7849340</v>
       </c>
       <c r="B211" s="1">
-        <v>2724.6830569399658</v>
+        <v>3291.9651213133438</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
@@ -2118,7 +2120,7 @@
         <v>7849341</v>
       </c>
       <c r="B212" s="1">
-        <v>5255.5575033005016</v>
+        <v>6388.573196526846</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
@@ -2126,7 +2128,7 @@
         <v>7849343</v>
       </c>
       <c r="B213" s="1">
-        <v>1880.6804128741608</v>
+        <v>2277.3617387626236</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
@@ -2134,7 +2136,7 @@
         <v>7849344</v>
       </c>
       <c r="B214" s="1">
-        <v>2661.0751687851803</v>
+        <v>3227.6544715472296</v>
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
@@ -2142,7 +2144,7 @@
         <v>7903303</v>
       </c>
       <c r="B215" s="1">
-        <v>3485.9459935219243</v>
+        <v>3963.5034506100019</v>
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
@@ -2150,7 +2152,7 @@
         <v>7903313</v>
       </c>
       <c r="B216" s="1">
-        <v>2794.6039712657357</v>
+        <v>3329.6715014013648</v>
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
@@ -2158,7 +2160,7 @@
         <v>7903327</v>
       </c>
       <c r="B217" s="1">
-        <v>4042.9668333512327</v>
+        <v>4371.5542263210928</v>
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
@@ -2166,7 +2168,7 @@
         <v>7903337</v>
       </c>
       <c r="B218" s="1">
-        <v>4010.1152139530213</v>
+        <v>4338.1451332833012</v>
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
@@ -2174,7 +2176,7 @@
         <v>7903339</v>
       </c>
       <c r="B219" s="1">
-        <v>1661.8132630888517</v>
+        <v>1899.7327413645837</v>
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
@@ -2182,7 +2184,7 @@
         <v>7903343</v>
       </c>
       <c r="B220" s="1">
-        <v>2313.9764293933604</v>
+        <v>2646.5724004634149</v>
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
@@ -2190,7 +2192,7 @@
         <v>7903344</v>
       </c>
       <c r="B221" s="1">
-        <v>3278.3042639205796</v>
+        <v>3753.316271442276</v>
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
@@ -2198,7 +2200,7 @@
         <v>7903341</v>
       </c>
       <c r="B222" s="1">
-        <v>6395.3852015589246</v>
+        <v>7343.3946169966057</v>
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
@@ -2206,7 +2208,7 @@
         <v>2909165</v>
       </c>
       <c r="B223" s="1">
-        <v>1563.0401040708607</v>
+        <v>1784.2033266287576</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
@@ -2214,7 +2216,7 @@
         <v>2909175</v>
       </c>
       <c r="B224" s="1">
-        <v>3022.1997766491972</v>
+        <v>3463.958546453624</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
@@ -2222,7 +2224,7 @@
         <v>6488184</v>
       </c>
       <c r="B225" s="1">
-        <v>2293.6983741000022</v>
+        <v>3339.0644020408604</v>
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
@@ -2230,7 +2232,7 @@
         <v>6489184</v>
       </c>
       <c r="B226" s="1">
-        <v>1834.450950843001</v>
+        <v>2706.7362390645712</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
@@ -2238,7 +2240,7 @@
         <v>7584165</v>
       </c>
       <c r="B227" s="1">
-        <v>1399.9761175895037</v>
+        <v>1620.0698208020174</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
@@ -2246,7 +2248,7 @@
         <v>7584175</v>
       </c>
       <c r="B228" s="1">
-        <v>2800.1050632395741</v>
+        <v>3240.3435474893972</v>
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
@@ -2254,7 +2256,7 @@
         <v>7584184</v>
       </c>
       <c r="B229" s="1">
-        <v>5111.5299633309232</v>
+        <v>5988.7873989713889</v>
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
@@ -2262,7 +2264,7 @@
         <v>7584185</v>
       </c>
       <c r="B230" s="1">
-        <v>2555.7649816654603</v>
+        <v>2994.393699485694</v>
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
@@ -2270,7 +2272,7 @@
         <v>7607185</v>
       </c>
       <c r="B231" s="1">
-        <v>1844.865710174593</v>
+        <v>2279.0507147333115</v>
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
@@ -2278,7 +2280,7 @@
         <v>2914165</v>
       </c>
       <c r="B232" s="1">
-        <v>2005.5697470695579</v>
+        <v>2229.5954886167888</v>
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
@@ -2286,7 +2288,7 @@
         <v>2914175</v>
       </c>
       <c r="B233" s="1">
-        <v>3843.6683728879948</v>
+        <v>4290.6538197422915</v>
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
@@ -2294,7 +2296,7 @@
         <v>7607184</v>
       </c>
       <c r="B234" s="1">
-        <v>3689.7314203491869</v>
+        <v>4558.1014294666229</v>
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
@@ -2302,7 +2304,7 @@
         <v>3001265</v>
       </c>
       <c r="B235" s="1">
-        <v>2631.3975550193431</v>
+        <v>5089.5907716929132</v>
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
@@ -2310,7 +2312,7 @@
         <v>3002265</v>
       </c>
       <c r="B236" s="1">
-        <v>2692.1752216556938</v>
+        <v>5150.5051919082971</v>
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
@@ -2318,7 +2320,7 @@
         <v>3006234</v>
       </c>
       <c r="B237" s="1">
-        <v>3001.0567234144714</v>
+        <v>5529.1594418184213</v>
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
@@ -2326,7 +2328,7 @@
         <v>3006265</v>
       </c>
       <c r="B238" s="1">
-        <v>2768.1400552257378</v>
+        <v>5365.2196159510704</v>
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
@@ -2334,7 +2336,7 @@
         <v>3020265</v>
       </c>
       <c r="B239" s="1">
-        <v>3909.4035119047039</v>
+        <v>5209.9806909651024</v>
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
@@ -2342,7 +2344,7 @@
         <v>3614265</v>
       </c>
       <c r="B240" s="1">
-        <v>3780.5887517996557</v>
+        <v>5660.0829422691304</v>
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
@@ -2350,7 +2352,7 @@
         <v>3617265</v>
       </c>
       <c r="B241" s="1">
-        <v>3910.5741189698097</v>
+        <v>5489.3651531796895</v>
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
@@ -2358,7 +2360,7 @@
         <v>3040265</v>
       </c>
       <c r="B242" s="1">
-        <v>2570.3354210800017</v>
+        <v>4283.4982706460023</v>
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
@@ -2366,7 +2368,7 @@
         <v>3057265</v>
       </c>
       <c r="B243" s="1">
-        <v>5061.3757313520309</v>
+        <v>5126.0613520928018</v>
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
@@ -2374,7 +2376,7 @@
         <v>3059265</v>
       </c>
       <c r="B244" s="1">
-        <v>4320.944237186608</v>
+        <v>5548.1746623066101</v>
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
@@ -2382,7 +2384,7 @@
         <v>3064265</v>
       </c>
       <c r="B245" s="1">
-        <v>4927.3284709946302</v>
+        <v>5834.2927795836777</v>
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
@@ -2390,7 +2392,7 @@
         <v>3084265</v>
       </c>
       <c r="B246" s="1">
-        <v>3142.7282674262433</v>
+        <v>5485.06516480966</v>
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
@@ -2398,7 +2400,7 @@
         <v>4501265</v>
       </c>
       <c r="B247" s="1">
-        <v>3080.9648006943899</v>
+        <v>5168.6567679603731</v>
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
@@ -2406,7 +2408,7 @@
         <v>7403265</v>
       </c>
       <c r="B248" s="1">
-        <v>3401.3842489723579</v>
+        <v>4262.2958927314594</v>
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
@@ -2470,7 +2472,7 @@
         <v>7330242</v>
       </c>
       <c r="B256" s="1">
-        <v>554.84075544170014</v>
+        <v>887.85235098560054</v>
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
@@ -2478,7 +2480,7 @@
         <v>7330265</v>
       </c>
       <c r="B257" s="1">
-        <v>1076.5566896630007</v>
+        <v>1694.9967388200012</v>
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
@@ -2486,7 +2488,7 @@
         <v>2874152</v>
       </c>
       <c r="B258" s="1">
-        <v>2753.961808356954</v>
+        <v>3878.0823190189253</v>
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
@@ -2494,7 +2496,7 @@
         <v>2874184</v>
       </c>
       <c r="B259" s="1">
-        <v>3059.6042341124221</v>
+        <v>4308.7924716490515</v>
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
@@ -2502,7 +2504,7 @@
         <v>7364184</v>
       </c>
       <c r="B260" s="1">
-        <v>3144.4206272091224</v>
+        <v>4258.9231579911266</v>
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
@@ -2510,7 +2512,7 @@
         <v>7364203</v>
       </c>
       <c r="B261" s="1">
-        <v>1886.6414360391502</v>
+        <v>2555.6098635858584</v>
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
@@ -2518,7 +2520,7 @@
         <v>7364234</v>
       </c>
       <c r="B262" s="1">
-        <v>3144.402393398585</v>
+        <v>4259.3497726430978</v>
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
@@ -2526,7 +2528,7 @@
         <v>7364242</v>
       </c>
       <c r="B263" s="1">
-        <v>1572.2331058677325</v>
+        <v>2129.6603426402316</v>
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
@@ -2534,7 +2536,7 @@
         <v>7364251</v>
       </c>
       <c r="B264" s="1">
-        <v>1179.1508975244692</v>
+        <v>1597.1359854545437</v>
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
@@ -2542,7 +2544,7 @@
         <v>7364256</v>
       </c>
       <c r="B265" s="1">
-        <v>2358.3496588015996</v>
+        <v>3194.4905139603475</v>
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
@@ -2550,7 +2552,7 @@
         <v>7364265</v>
       </c>
       <c r="B266" s="1">
-        <v>3144.4662117354655</v>
+        <v>4259.3206852804633</v>
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
@@ -2558,7 +2560,7 @@
         <v>7370184</v>
       </c>
       <c r="B267" s="1">
-        <v>3444.5491486580186</v>
+        <v>4578.699927006176</v>
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
@@ -2566,7 +2568,7 @@
         <v>7370234</v>
       </c>
       <c r="B268" s="1">
-        <v>3444.1206541103847</v>
+        <v>4578.5447944054586</v>
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
@@ -2574,7 +2576,7 @@
         <v>7370242</v>
       </c>
       <c r="B269" s="1">
-        <v>1722.311041950084</v>
+        <v>2289.2772450965017</v>
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
@@ -2582,7 +2584,7 @@
         <v>7370251</v>
       </c>
       <c r="B270" s="1">
-        <v>1291.7332814625634</v>
+        <v>1717.022168414861</v>
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
@@ -2590,78 +2592,78 @@
         <v>7370256</v>
       </c>
       <c r="B271" s="1">
-        <v>2583.4665629251267</v>
+        <v>3433.9158676447523</v>
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="2">
         <v>7376184</v>
       </c>
-      <c r="B272" s="2">
-        <v>3096.1557307160947</v>
+      <c r="B272" s="1">
+        <v>3807.2739825792528</v>
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="2">
         <v>7376251</v>
       </c>
-      <c r="B273" s="2">
-        <v>1161.1746395607129</v>
+      <c r="B273" s="1">
+        <v>1432.4544883742474</v>
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="2">
         <v>2960401</v>
       </c>
-      <c r="B274" s="2">
-        <v>133065.73840559999</v>
+      <c r="B274" s="1">
+        <v>142783.1349945</v>
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="2">
         <v>2960401</v>
       </c>
-      <c r="B275" s="2">
-        <v>133065.73840559999</v>
+      <c r="B275" s="1">
+        <v>142783.1349945</v>
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="2">
         <v>7427401</v>
       </c>
-      <c r="B276" s="2">
-        <v>68915.120274000001</v>
+      <c r="B276" s="1">
+        <v>74658.046963500004</v>
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="2">
         <v>7428401</v>
       </c>
-      <c r="B277" s="2">
-        <v>76495.78350414001</v>
+      <c r="B277" s="1">
+        <v>82238.710193639999</v>
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="2">
         <v>7670401</v>
       </c>
-      <c r="B278" s="2">
-        <v>50537.754867600001</v>
+      <c r="B278" s="1">
+        <v>56280.681557099997</v>
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="2">
         <v>7688401</v>
       </c>
-      <c r="B279" s="2">
-        <v>53524.076746139996</v>
+      <c r="B279" s="1">
+        <v>59267.003435639999</v>
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="2">
         <v>2968401</v>
       </c>
-      <c r="B280" s="2">
+      <c r="B280" s="1">
         <v>59726.437570800001</v>
       </c>
     </row>
@@ -2669,7 +2671,7 @@
       <c r="A281" s="2">
         <v>7205401</v>
       </c>
-      <c r="B281" s="2">
+      <c r="B281" s="1">
         <v>79252.388315100005</v>
       </c>
     </row>
@@ -2677,7 +2679,7 @@
       <c r="A282" s="2">
         <v>7420401</v>
       </c>
-      <c r="B282" s="2">
+      <c r="B282" s="1">
         <v>73968.895760760002</v>
       </c>
     </row>
@@ -2685,7 +2687,7 @@
       <c r="A283" s="2">
         <v>7421401</v>
       </c>
-      <c r="B283" s="2">
+      <c r="B283" s="1">
         <v>83617.012599120004</v>
       </c>
     </row>
@@ -2693,7 +2695,7 @@
       <c r="A284" s="2">
         <v>7477401</v>
       </c>
-      <c r="B284" s="2">
+      <c r="B284" s="1">
         <v>61793.891179020007</v>
       </c>
     </row>
@@ -2701,7 +2703,7 @@
       <c r="A285" s="2">
         <v>7209401</v>
       </c>
-      <c r="B285" s="2">
+      <c r="B285" s="1">
         <v>178949.59564481999</v>
       </c>
     </row>
@@ -2709,7 +2711,7 @@
       <c r="A286" s="2">
         <v>7202271</v>
       </c>
-      <c r="B286" s="2">
+      <c r="B286" s="1">
         <v>16818.571019250001</v>
       </c>
     </row>
@@ -2717,7 +2719,7 @@
       <c r="A287" s="2">
         <v>7206271</v>
       </c>
-      <c r="B287" s="2">
+      <c r="B287" s="1">
         <v>15850.477663019998</v>
       </c>
     </row>
@@ -2725,7 +2727,7 @@
       <c r="A288" s="2">
         <v>7207271</v>
       </c>
-      <c r="B288" s="2">
+      <c r="B288" s="1">
         <v>14422.95017163</v>
       </c>
     </row>
@@ -2733,7 +2735,7 @@
       <c r="A289" s="2">
         <v>7208271</v>
       </c>
-      <c r="B289" s="2">
+      <c r="B289" s="1">
         <v>15533.249331600002</v>
       </c>
     </row>
@@ -2741,7 +2743,7 @@
       <c r="A290" s="2">
         <v>7202401</v>
       </c>
-      <c r="B290" s="2">
+      <c r="B290" s="1">
         <v>70637.998280850006</v>
       </c>
     </row>
@@ -2749,7 +2751,7 @@
       <c r="A291" s="2">
         <v>7206401</v>
       </c>
-      <c r="B291" s="2">
+      <c r="B291" s="1">
         <v>66572.006184683996</v>
       </c>
     </row>
@@ -2757,7 +2759,7 @@
       <c r="A292" s="2">
         <v>7207401</v>
       </c>
-      <c r="B292" s="2">
+      <c r="B292" s="1">
         <v>60576.390720846</v>
       </c>
     </row>
@@ -2765,7 +2767,7 @@
       <c r="A293" s="2">
         <v>7208401</v>
       </c>
-      <c r="B293" s="2">
+      <c r="B293" s="1">
         <v>65239.647192719996</v>
       </c>
     </row>
@@ -2773,440 +2775,440 @@
       <c r="A294" s="2">
         <v>7264401</v>
       </c>
-      <c r="B294" s="2">
-        <v>63105.344702399998</v>
+      <c r="B294" s="1">
+        <v>69833.988544320004</v>
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="2">
         <v>7267401</v>
       </c>
-      <c r="B295" s="2">
-        <v>146751.5277228</v>
+      <c r="B295" s="1">
+        <v>159193.92783294001</v>
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="2">
         <v>7265401</v>
       </c>
-      <c r="B296" s="2">
-        <v>92056.987822800002</v>
+      <c r="B296" s="1">
+        <v>101764.66093794</v>
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="2">
         <v>1301401</v>
       </c>
-      <c r="B297" s="2">
-        <v>42417.438843779993</v>
+      <c r="B297" s="1">
+        <v>52054.616774160007</v>
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="2">
         <v>1404401</v>
       </c>
-      <c r="B298" s="2">
-        <v>50916.970344239999</v>
+      <c r="B298" s="1">
+        <v>63766.540918079998</v>
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="2">
         <v>7436401</v>
       </c>
-      <c r="B299" s="2">
-        <v>53138.784098399992</v>
+      <c r="B299" s="1">
+        <v>62929.106740499999</v>
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="2">
         <v>7470401</v>
       </c>
-      <c r="B300" s="2">
-        <v>43282.828008420009</v>
+      <c r="B300" s="1">
+        <v>52424.108777039997</v>
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="2">
         <v>7472401</v>
       </c>
-      <c r="B301" s="2">
-        <v>42850.133426100001</v>
+      <c r="B301" s="1">
+        <v>52725.536463599994</v>
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="2">
         <v>7485401</v>
       </c>
-      <c r="B302" s="2">
-        <v>39730.113783360008</v>
+      <c r="B302" s="1">
+        <v>49609.163123520004</v>
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="2">
         <v>7489271</v>
       </c>
-      <c r="B303" s="2">
-        <v>12223.506194900001</v>
+      <c r="B303" s="1">
+        <v>14479.583618500001</v>
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="2">
         <v>7489401</v>
       </c>
-      <c r="B304" s="2">
-        <v>50879.29188342001</v>
+      <c r="B304" s="1">
+        <v>60364.540536300003</v>
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="2">
         <v>7494401</v>
       </c>
-      <c r="B305" s="2">
-        <v>49159.452462120003</v>
+      <c r="B305" s="1">
+        <v>58039.414873439993</v>
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="2">
         <v>7577271</v>
       </c>
-      <c r="B306" s="2">
-        <v>10997.364578199999</v>
+      <c r="B306" s="1">
+        <v>13226.2394264</v>
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="2">
         <v>7577401</v>
       </c>
-      <c r="B307" s="2">
-        <v>45959.21416086</v>
+      <c r="B307" s="1">
+        <v>55078.617113520006</v>
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="2">
         <v>7612401</v>
       </c>
-      <c r="B308" s="2">
-        <v>46594.886257920007</v>
+      <c r="B308" s="1">
+        <v>55705.781171039991</v>
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="2">
         <v>2502401</v>
       </c>
-      <c r="B309" s="2">
-        <v>47500.384751820005</v>
+      <c r="B309" s="1">
+        <v>56848.289337839997</v>
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="2">
         <v>2503401</v>
       </c>
-      <c r="B310" s="2">
-        <v>52391.292053099998</v>
+      <c r="B310" s="1">
+        <v>61719.749691600002</v>
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="2">
         <v>4906401</v>
       </c>
-      <c r="B311" s="2">
-        <v>39297.41920104</v>
+      <c r="B311" s="1">
+        <v>49910.590810080001</v>
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="2">
         <v>4925401</v>
       </c>
-      <c r="B312" s="2">
-        <v>44484.892452000007</v>
+      <c r="B312" s="1">
+        <v>53624.957786400002</v>
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="2">
         <v>7511401</v>
       </c>
-      <c r="B313" s="2">
-        <v>49567.838360039997</v>
+      <c r="B313" s="1">
+        <v>58904.804038079994</v>
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="2">
         <v>7515401</v>
       </c>
-      <c r="B314" s="2">
-        <v>51338.726018579997</v>
+      <c r="B314" s="1">
+        <v>60659.891051760002</v>
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="2">
         <v>4950288</v>
       </c>
-      <c r="B315" s="2">
-        <v>4645.0886241759999</v>
+      <c r="B315" s="1">
+        <v>6105.9711032320001</v>
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="2">
         <v>4950401</v>
       </c>
-      <c r="B316" s="2">
-        <v>45483.979380839992</v>
+      <c r="B316" s="1">
+        <v>54383.388739679991</v>
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="2">
         <v>7651401</v>
       </c>
-      <c r="B317" s="2">
-        <v>36295.296677639999</v>
+      <c r="B317" s="1">
+        <v>45483.979380839992</v>
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="2">
         <v>2900401</v>
       </c>
-      <c r="B318" s="2">
-        <v>54897.7848102684</v>
+      <c r="B318" s="1">
+        <v>63747.385674772799</v>
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="2">
         <v>2900403</v>
       </c>
-      <c r="B319" s="2">
-        <v>54897.7848102684</v>
+      <c r="B319" s="1">
+        <v>63747.385674772799</v>
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="2">
         <v>7701451</v>
       </c>
-      <c r="B320" s="2">
-        <v>46285.355676560001</v>
+      <c r="B320" s="1">
+        <v>53932.867788800009</v>
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="2">
         <v>7705451</v>
       </c>
-      <c r="B321" s="2">
-        <v>46380.159545720009</v>
+      <c r="B321" s="1">
+        <v>54017.137894719999</v>
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="2">
         <v>7727451</v>
       </c>
-      <c r="B322" s="2">
-        <v>62075.466773320011</v>
+      <c r="B322" s="1">
+        <v>70038.991782759986</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="2">
         <v>7849451</v>
       </c>
-      <c r="B323" s="2">
-        <v>65830.753368379999</v>
+      <c r="B323" s="1">
+        <v>73378.194729840005</v>
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="2">
         <v>7903451</v>
       </c>
-      <c r="B324" s="2">
-        <v>64777.377044379995</v>
+      <c r="B324" s="1">
+        <v>73372.927848220017</v>
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="2">
         <v>7584401</v>
       </c>
-      <c r="B325" s="2">
-        <v>45622.538881920002</v>
+      <c r="B325" s="1">
+        <v>54864.700690799997</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="2">
         <v>2909401</v>
       </c>
-      <c r="B326" s="2">
-        <v>57251.813498879994</v>
+      <c r="B326" s="1">
+        <v>66557.1778872</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="2">
         <v>7742451</v>
       </c>
-      <c r="B327" s="2">
-        <v>46180.018044160002</v>
+      <c r="B327" s="1">
+        <v>63371.119651840003</v>
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="2">
         <v>3040288</v>
       </c>
-      <c r="B328" s="2">
-        <v>3280.5148376000002</v>
+      <c r="B328" s="1">
+        <v>5507.6533512000005</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="2">
         <v>3006271</v>
       </c>
-      <c r="B329" s="2">
-        <v>6975.434866399999</v>
+      <c r="B329" s="1">
+        <v>13492.477398399998</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="2">
         <v>3006288</v>
       </c>
-      <c r="B330" s="2">
-        <v>3655.5168089439999</v>
+      <c r="B330" s="1">
+        <v>7044.3789255840011</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="2">
         <v>3001401</v>
       </c>
-      <c r="B331" s="2">
-        <v>27566.0481096</v>
+      <c r="B331" s="1">
+        <v>45700.326671999996</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="2">
         <v>3002401</v>
       </c>
-      <c r="B332" s="2">
-        <v>28951.6431204</v>
+      <c r="B332" s="1">
+        <v>46842.834838800001</v>
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="2">
         <v>3006401</v>
       </c>
-      <c r="B333" s="2">
-        <v>29291.964702000001</v>
+      <c r="B333" s="1">
+        <v>49127.851172399998</v>
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="2">
         <v>3007403</v>
       </c>
-      <c r="B334" s="2">
-        <v>35101.7402736</v>
+      <c r="B334" s="1">
+        <v>57125.408339999994</v>
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="2">
         <v>3020401</v>
       </c>
-      <c r="B335" s="2">
-        <v>39652.325993279999</v>
+      <c r="B335" s="1">
+        <v>54383.388739679991</v>
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="2">
         <v>3017401</v>
       </c>
-      <c r="B336" s="2">
-        <v>43410.448601520009</v>
+      <c r="B336" s="1">
+        <v>56439.903439919995</v>
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="2">
         <v>3019401</v>
       </c>
-      <c r="B337" s="2">
-        <v>37080.467183759996</v>
+      <c r="B337" s="1">
+        <v>52783.87730616</v>
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="2">
         <v>3064401</v>
       </c>
-      <c r="B338" s="2">
-        <v>41271.284374320006</v>
+      <c r="B338" s="1">
+        <v>51869.870772720002</v>
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="2">
         <v>3081401</v>
       </c>
-      <c r="B339" s="2">
-        <v>44786.320138560004</v>
+      <c r="B339" s="1">
+        <v>53926.385472959999</v>
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="2">
         <v>3082401</v>
       </c>
-      <c r="B340" s="2">
-        <v>32315.965041359999</v>
+      <c r="B340" s="1">
+        <v>55068.893639759997</v>
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="2">
         <v>3084401</v>
       </c>
-      <c r="B341" s="2">
-        <v>31683.939246960002</v>
+      <c r="B341" s="1">
+        <v>57353.909973360001</v>
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="2">
         <v>3121401</v>
       </c>
-      <c r="B342" s="2">
-        <v>45700.326671999996</v>
+      <c r="B342" s="1">
+        <v>54840.392006400005</v>
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="2">
         <v>3122401</v>
       </c>
-      <c r="B343" s="2">
-        <v>46842.834838800001</v>
+      <c r="B343" s="1">
+        <v>55982.900173199996</v>
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="2">
         <v>3614401</v>
       </c>
-      <c r="B344" s="2">
-        <v>37916.685927120001</v>
+      <c r="B344" s="1">
+        <v>58724.919773520007</v>
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="2">
         <v>3617401</v>
       </c>
-      <c r="B345" s="2">
-        <v>39248.801832239995</v>
+      <c r="B345" s="1">
+        <v>56896.906706639988</v>
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="2">
         <v>3923401</v>
       </c>
-      <c r="B346" s="2">
-        <v>33725.868736559998</v>
+      <c r="B346" s="1">
+        <v>48213.844638960007</v>
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="2">
         <v>4803401</v>
       </c>
-      <c r="B347" s="2">
-        <v>26588.838996719998</v>
+      <c r="B347" s="1">
+        <v>49584.854439119998</v>
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="2">
         <v>4811401</v>
       </c>
-      <c r="B348" s="2">
-        <v>31260.968138400003</v>
+      <c r="B348" s="1">
+        <v>52555.375672800001</v>
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
@@ -3214,7 +3216,7 @@
         <v>4501401</v>
       </c>
       <c r="B349" s="1">
-        <v>29559.360230399998</v>
+        <v>52555.375672800001</v>
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
@@ -3222,7 +3224,7 @@
         <v>7403401</v>
       </c>
       <c r="B350" s="1">
-        <v>27420.196003200002</v>
+        <v>36560.261337600001</v>
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
@@ -3230,23 +3232,15 @@
         <v>7330403</v>
       </c>
       <c r="B351" s="1">
-        <v>10374.94650192</v>
+        <v>16772.992236000002</v>
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
-        <v>7577240</v>
-      </c>
-      <c r="B352" s="1">
-        <v>4058.97</v>
-      </c>
-    </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353" s="1">
         <v>7079401</v>
       </c>
-      <c r="B353" s="3">
-        <v>87758.9</v>
+      <c r="B352" s="3">
+        <v>92999.54</v>
       </c>
     </row>
   </sheetData>
